--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -39,90 +39,90 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelarco</t>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
   </si>
   <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parral</t>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
   </si>
   <si>
     <t xml:space="preserve">Curepto</t>
   </si>
   <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
   </si>
   <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
+    <t xml:space="preserve">Curicó</t>
   </si>
   <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13.24</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7403</v>
+        <v>7110</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.95</v>
+        <v>8.05</v>
       </c>
     </row>
     <row r="4">
@@ -593,16 +593,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.37</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="5">
@@ -610,16 +610,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7106</v>
+        <v>7108</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9.16</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="6">
@@ -627,16 +627,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7402</v>
+        <v>7403</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.61</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="7">
@@ -644,16 +644,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7309</v>
+        <v>7306</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7.44</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="8">
@@ -661,16 +661,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7108</v>
+        <v>7107</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7.38</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="9">
@@ -678,16 +678,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7408</v>
+        <v>7302</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6.34</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="10">
@@ -695,16 +695,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7407</v>
+        <v>7307</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -712,16 +712,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7404</v>
+        <v>7402</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.95</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="12">
@@ -729,16 +729,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7103</v>
+        <v>7407</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.81</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="13">
@@ -746,16 +746,16 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7405</v>
+        <v>7408</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.79</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14">
@@ -763,16 +763,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7302</v>
+        <v>7404</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.46</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="15">
@@ -780,16 +780,16 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7306</v>
+        <v>7303</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.44</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="16">
@@ -797,16 +797,16 @@
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7303</v>
+        <v>7304</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.11</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="17">
@@ -814,16 +814,16 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7109</v>
+        <v>7406</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.06</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="18">
@@ -831,16 +831,16 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7406</v>
+        <v>7109</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3.79</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="19">
@@ -848,16 +848,16 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7305</v>
+        <v>7308</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="20">
@@ -865,16 +865,16 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7307</v>
+        <v>7309</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="21">
@@ -882,16 +882,16 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7110</v>
+        <v>7405</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="22">
@@ -899,16 +899,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7201</v>
+        <v>7401</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="23">
@@ -916,16 +916,16 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7202</v>
+        <v>7105</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="24">
@@ -936,13 +936,13 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7308</v>
+        <v>7103</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="25">
@@ -953,13 +953,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7304</v>
+        <v>7102</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.95</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="26">
@@ -970,13 +970,13 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7101</v>
+        <v>7201</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="27">
@@ -987,13 +987,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7401</v>
+        <v>7202</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="28">
@@ -1004,13 +1004,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7301</v>
+        <v>7305</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="29">
@@ -1021,13 +1021,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7102</v>
+        <v>7301</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.25</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="30">
@@ -1038,13 +1038,13 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7104</v>
+        <v>7101</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.44</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="31">
@@ -1055,13 +1055,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7107</v>
+        <v>7104</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-1.06</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.4</v>
+        <v>83.99</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.05</v>
+        <v>80.52</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.83</v>
+        <v>78.26</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.91</v>
+        <v>69.05</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.53</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.51</v>
+        <v>65.07</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.88</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5.59</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.98</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3.92</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.6</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.39</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="15">
@@ -789,7 +789,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3.09</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.89</v>
+        <v>28.93</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.84</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.82</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2.78</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.55</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.12</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.08</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2.01</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.86</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.72</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.15</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.84</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="28">
@@ -1010,7 +1010,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.66</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.57</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.27</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-4</v>
+        <v>-40.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:27</t>
+    <t xml:space="preserve">2026-10-05 08:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
